--- a/artfynd/A 33846-2023 artfynd.xlsx
+++ b/artfynd/A 33846-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33846-2023 artfynd.xlsx
+++ b/artfynd/A 33846-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AY82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79435811</v>
+        <v>79438174</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461452.4400007116</v>
+        <v>461630</v>
       </c>
       <c r="R2" t="n">
-        <v>7075620.32141869</v>
+        <v>7075596</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,68 +756,48 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79435797</v>
+        <v>79435824</v>
       </c>
       <c r="B3" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461535.6864796501</v>
+        <v>461666</v>
       </c>
       <c r="R3" t="n">
-        <v>7075553.017578004</v>
+        <v>7075605</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,19 +840,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>79435789</v>
+        <v>79438186</v>
       </c>
       <c r="B4" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461482.1231230136</v>
+        <v>461451</v>
       </c>
       <c r="R4" t="n">
-        <v>7075587.257515782</v>
+        <v>7075608</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,19 +937,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,49 +954,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>79438199</v>
+        <v>79435823</v>
       </c>
       <c r="B5" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6463</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461538.4868780377</v>
+        <v>461605</v>
       </c>
       <c r="R5" t="n">
-        <v>7075564.914634661</v>
+        <v>7075562</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,21 +1034,11 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1122,31 +1047,41 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>79438176</v>
+        <v>79438187</v>
       </c>
       <c r="B6" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,21 +1089,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461657.9863948512</v>
+        <v>461447</v>
       </c>
       <c r="R6" t="n">
-        <v>7075603.667913369</v>
+        <v>7075703</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,19 +1146,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,37 +1175,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>79438173</v>
+        <v>79435806</v>
       </c>
       <c r="B7" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461657.7810243547</v>
+        <v>461619</v>
       </c>
       <c r="R7" t="n">
-        <v>7075623.113675742</v>
+        <v>7075584</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,21 +1243,11 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1346,53 +1256,63 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>79436255</v>
+        <v>79436289</v>
       </c>
       <c r="B8" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461554.8772706249</v>
+        <v>461514</v>
       </c>
       <c r="R8" t="n">
-        <v>7075530.245865598</v>
+        <v>7075562</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,19 +1355,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,37 +1384,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>79437707</v>
+        <v>79438191</v>
       </c>
       <c r="B9" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461527.5446244361</v>
+        <v>461434</v>
       </c>
       <c r="R9" t="n">
-        <v>7075538.534403487</v>
+        <v>7075631</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,19 +1452,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,53 +1481,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>79436279</v>
+        <v>79438192</v>
       </c>
       <c r="B10" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Järnsjöhön, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461638.4234202633</v>
+        <v>461519</v>
       </c>
       <c r="R10" t="n">
-        <v>7075595.952408353</v>
+        <v>7075591</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,55 +1549,39 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>79435824</v>
+        <v>79436296</v>
       </c>
       <c r="B11" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1718,21 +1589,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1742,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461665.971285095</v>
+        <v>461436</v>
       </c>
       <c r="R11" t="n">
-        <v>7075605.338138262</v>
+        <v>7075631</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,19 +1646,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1802,27 +1663,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>79435823</v>
+        <v>79435789</v>
       </c>
       <c r="B12" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,21 +1686,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1854,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461604.8273476248</v>
+        <v>461482</v>
       </c>
       <c r="R12" t="n">
-        <v>7075562.336344617</v>
+        <v>7075587</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1887,21 +1743,11 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1910,21 +1756,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1941,15 +1772,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>79438174</v>
+        <v>79436270</v>
       </c>
       <c r="B13" t="n">
-        <v>89338</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1957,21 +1783,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>112</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1981,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461630.4600547163</v>
+        <v>461416</v>
       </c>
       <c r="R13" t="n">
-        <v>7075596.049564297</v>
+        <v>7075649</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,19 +1840,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,49 +1857,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>79438190</v>
+        <v>79436271</v>
       </c>
       <c r="B14" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229748</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2093,10 +1904,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461579.9228462023</v>
+        <v>461510</v>
       </c>
       <c r="R14" t="n">
-        <v>7075588.270592876</v>
+        <v>7075563</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2126,19 +1937,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2153,49 +1954,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>79436284</v>
+        <v>79436272</v>
       </c>
       <c r="B15" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219880</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2205,10 +2001,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461622.7557671465</v>
+        <v>461636</v>
       </c>
       <c r="R15" t="n">
-        <v>7075581.119120113</v>
+        <v>7075589</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2238,19 +2034,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2277,15 +2063,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>79435806</v>
+        <v>79437300</v>
       </c>
       <c r="B16" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2293,21 +2074,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2317,10 +2098,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461618.8064215119</v>
+        <v>461510</v>
       </c>
       <c r="R16" t="n">
-        <v>7075583.818700708</v>
+        <v>7075554</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2350,21 +2131,11 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2373,68 +2144,48 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>79435793</v>
+        <v>79438175</v>
       </c>
       <c r="B17" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2444,10 +2195,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461438.0952583499</v>
+        <v>461538</v>
       </c>
       <c r="R17" t="n">
-        <v>7075641.266153938</v>
+        <v>7075570</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2477,19 +2228,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,49 +2245,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>79438172</v>
+        <v>79438176</v>
       </c>
       <c r="B18" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2556,10 +2292,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461657.9432974821</v>
+        <v>461658</v>
       </c>
       <c r="R18" t="n">
-        <v>7075600.133288103</v>
+        <v>7075604</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2589,19 +2325,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,15 +2354,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>79438171</v>
+        <v>79435790</v>
       </c>
       <c r="B19" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2644,21 +2365,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>2809</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2668,10 +2389,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461440.2476774091</v>
+        <v>461514</v>
       </c>
       <c r="R19" t="n">
-        <v>7075636.378974909</v>
+        <v>7075574</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2701,19 +2422,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2728,27 +2439,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>79438184</v>
+        <v>79435786</v>
       </c>
       <c r="B20" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2756,21 +2462,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6464</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2780,10 +2486,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461583.9045389916</v>
+        <v>461524</v>
       </c>
       <c r="R20" t="n">
-        <v>7075588.221948421</v>
+        <v>7075571</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2813,21 +2519,11 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2836,53 +2532,63 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>79436296</v>
+        <v>79435815</v>
       </c>
       <c r="B21" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2892,10 +2598,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461436.2010249906</v>
+        <v>461535</v>
       </c>
       <c r="R21" t="n">
-        <v>7075631.125916054</v>
+        <v>7075553</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2925,19 +2631,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2952,49 +2648,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>79437700</v>
+        <v>79435816</v>
       </c>
       <c r="B22" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3004,10 +2695,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461633.1899790656</v>
+        <v>461549</v>
       </c>
       <c r="R22" t="n">
-        <v>7075602.202776575</v>
+        <v>7075513</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3037,19 +2728,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3064,49 +2745,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>79435796</v>
+        <v>79435817</v>
       </c>
       <c r="B23" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3116,10 +2792,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461483.0187674894</v>
+        <v>461604</v>
       </c>
       <c r="R23" t="n">
-        <v>7075588.130338392</v>
+        <v>7075562</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3149,19 +2825,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3188,37 +2854,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>79435786</v>
+        <v>79435776</v>
       </c>
       <c r="B24" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3298</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3228,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461523.5205003457</v>
+        <v>461456</v>
       </c>
       <c r="R24" t="n">
-        <v>7075571.284307097</v>
+        <v>7075695</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3261,19 +2922,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3315,37 +2966,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>79436259</v>
+        <v>79435777</v>
       </c>
       <c r="B25" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3355,10 +3001,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461558.0331369621</v>
+        <v>461417</v>
       </c>
       <c r="R25" t="n">
-        <v>7075498.831926269</v>
+        <v>7075690</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3388,21 +3034,11 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3411,53 +3047,63 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>79438189</v>
+        <v>79435778</v>
       </c>
       <c r="B26" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229748</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3467,10 +3113,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461570.2272705563</v>
+        <v>461438</v>
       </c>
       <c r="R26" t="n">
-        <v>7075555.246685448</v>
+        <v>7075625</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3500,21 +3146,11 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3523,31 +3159,41 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>79438193</v>
+        <v>79435779</v>
       </c>
       <c r="B27" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3555,21 +3201,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3579,10 +3225,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461591.8193566168</v>
+        <v>461469</v>
       </c>
       <c r="R27" t="n">
-        <v>7075584.148201088</v>
+        <v>7075626</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3612,21 +3258,11 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3635,53 +3271,63 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>79438200</v>
+        <v>79435780</v>
       </c>
       <c r="B28" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3691,10 +3337,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461587.7944825452</v>
+        <v>461529</v>
       </c>
       <c r="R28" t="n">
-        <v>7075580.662188183</v>
+        <v>7075561</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3724,21 +3370,11 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3747,31 +3383,41 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>79435816</v>
+        <v>79435781</v>
       </c>
       <c r="B29" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3779,21 +3425,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3803,10 +3449,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>461548.9151350789</v>
+        <v>461642</v>
       </c>
       <c r="R29" t="n">
-        <v>7075513.084445971</v>
+        <v>7075599</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3836,21 +3482,11 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3859,6 +3495,21 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3875,15 +3526,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>79435780</v>
+        <v>79436254</v>
       </c>
       <c r="B30" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3915,10 +3561,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>461529.142139833</v>
+        <v>461455</v>
       </c>
       <c r="R30" t="n">
-        <v>7075560.609943334</v>
+        <v>7075697</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3948,21 +3594,11 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3971,68 +3607,48 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>79436277</v>
+        <v>79436255</v>
       </c>
       <c r="B31" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4042,10 +3658,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>461507.9008496974</v>
+        <v>461555</v>
       </c>
       <c r="R31" t="n">
-        <v>7075560.427973946</v>
+        <v>7075530</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4075,19 +3691,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4114,15 +3720,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>79436271</v>
+        <v>79436256</v>
       </c>
       <c r="B32" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4130,21 +3731,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4154,10 +3755,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>461510.1399606078</v>
+        <v>461577</v>
       </c>
       <c r="R32" t="n">
-        <v>7075562.61006742</v>
+        <v>7075534</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4187,19 +3788,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4226,15 +3817,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>79436254</v>
+        <v>79437700</v>
       </c>
       <c r="B33" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4266,10 +3852,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>461455.146550215</v>
+        <v>461633</v>
       </c>
       <c r="R33" t="n">
-        <v>7075696.734639765</v>
+        <v>7075602</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4299,19 +3885,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4326,49 +3902,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>79436300</v>
+        <v>79437706</v>
       </c>
       <c r="B34" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4378,10 +3949,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>461636.1359110515</v>
+        <v>461401</v>
       </c>
       <c r="R34" t="n">
-        <v>7075589.79378207</v>
+        <v>7075680</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4411,19 +3982,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4438,27 +3999,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>79435815</v>
+        <v>79437707</v>
       </c>
       <c r="B35" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4466,21 +4022,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4490,10 +4046,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>461534.8070535356</v>
+        <v>461528</v>
       </c>
       <c r="R35" t="n">
-        <v>7075553.47023601</v>
+        <v>7075539</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4523,19 +4079,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4550,49 +4096,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>79436260</v>
+        <v>79438165</v>
       </c>
       <c r="B36" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4602,10 +4143,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>461459.318136737</v>
+        <v>461440</v>
       </c>
       <c r="R36" t="n">
-        <v>7075603.887063771</v>
+        <v>7075700</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4635,19 +4176,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4662,49 +4193,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>79436267</v>
+        <v>79438166</v>
       </c>
       <c r="B37" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4714,10 +4240,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>461459.28564623</v>
+        <v>461581</v>
       </c>
       <c r="R37" t="n">
-        <v>7075601.236094888</v>
+        <v>7075552</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4747,19 +4273,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4774,49 +4290,44 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>79436288</v>
+        <v>79438167</v>
       </c>
       <c r="B38" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229748</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4826,10 +4337,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>461627.1259652247</v>
+        <v>461603</v>
       </c>
       <c r="R38" t="n">
-        <v>7075576.646817321</v>
+        <v>7075589</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4859,19 +4370,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4886,12 +4387,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4901,12 +4402,7 @@
         <v>79436275</v>
       </c>
       <c r="B39" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4938,10 +4434,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>461509.6705067201</v>
+        <v>461510</v>
       </c>
       <c r="R39" t="n">
-        <v>7075560.40631308</v>
+        <v>7075560</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4971,19 +4467,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5010,15 +4496,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>79436264</v>
+        <v>79435787</v>
       </c>
       <c r="B40" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5050,10 +4531,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>461507.4422105391</v>
+        <v>461449</v>
       </c>
       <c r="R40" t="n">
-        <v>7075559.107886944</v>
+        <v>7075618</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5083,19 +4564,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5110,49 +4581,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>79436289</v>
+        <v>79436259</v>
       </c>
       <c r="B41" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5162,10 +4628,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>461514.1108714188</v>
+        <v>461558</v>
       </c>
       <c r="R41" t="n">
-        <v>7075561.677667119</v>
+        <v>7075499</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5195,19 +4661,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5234,37 +4690,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>79435778</v>
+        <v>79436260</v>
       </c>
       <c r="B42" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5274,10 +4725,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>461438.3426122295</v>
+        <v>461459</v>
       </c>
       <c r="R42" t="n">
-        <v>7075625.355070272</v>
+        <v>7075604</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5307,21 +4758,11 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5330,46 +4771,26 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>79435787</v>
+        <v>79436261</v>
       </c>
       <c r="B43" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5401,10 +4822,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>461449.3160773031</v>
+        <v>461572</v>
       </c>
       <c r="R43" t="n">
-        <v>7075618.150253334</v>
+        <v>7075510</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5434,19 +4855,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5461,49 +4872,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>79438167</v>
+        <v>79436262</v>
       </c>
       <c r="B44" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5513,10 +4919,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>461602.5019575043</v>
+        <v>461422</v>
       </c>
       <c r="R44" t="n">
-        <v>7075589.320497744</v>
+        <v>7075663</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5546,19 +4952,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5573,27 +4969,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>79436299</v>
+        <v>79436263</v>
       </c>
       <c r="B45" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5601,21 +4992,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5625,10 +5016,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>461468.1663000641</v>
+        <v>461478</v>
       </c>
       <c r="R45" t="n">
-        <v>7075603.778632346</v>
+        <v>7075577</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5658,19 +5049,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5697,37 +5078,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>79438191</v>
+        <v>79436264</v>
       </c>
       <c r="B46" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1204</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5737,10 +5113,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>461433.9835846544</v>
+        <v>461507</v>
       </c>
       <c r="R46" t="n">
-        <v>7075630.711219937</v>
+        <v>7075559</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5770,19 +5146,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5797,27 +5163,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>79437304</v>
+        <v>79436265</v>
       </c>
       <c r="B47" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5825,21 +5186,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5849,10 +5210,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>461508.7261889186</v>
+        <v>461588</v>
       </c>
       <c r="R47" t="n">
-        <v>7075555.556965283</v>
+        <v>7075520</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5882,19 +5243,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5909,49 +5260,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>79435817</v>
+        <v>79436266</v>
       </c>
       <c r="B48" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5961,10 +5307,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>461604.3849336792</v>
+        <v>461630</v>
       </c>
       <c r="R48" t="n">
-        <v>7075562.341746354</v>
+        <v>7075590</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5994,19 +5340,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6021,27 +5357,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>79436265</v>
+        <v>79437296</v>
       </c>
       <c r="B49" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6073,10 +5404,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>461588.3823449036</v>
+        <v>461410</v>
       </c>
       <c r="R49" t="n">
-        <v>7075520.114525458</v>
+        <v>7075698</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6106,19 +5437,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6133,49 +5454,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>79437300</v>
+        <v>79437297</v>
       </c>
       <c r="B50" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6185,10 +5501,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>461510.4796250632</v>
+        <v>461496</v>
       </c>
       <c r="R50" t="n">
-        <v>7075554.209800462</v>
+        <v>7075547</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6218,19 +5534,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6257,15 +5563,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>79435794</v>
+        <v>79437298</v>
       </c>
       <c r="B51" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6273,21 +5574,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6297,10 +5598,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>461445.9339205667</v>
+        <v>461510</v>
       </c>
       <c r="R51" t="n">
-        <v>7075631.006571052</v>
+        <v>7075554</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6330,19 +5631,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6357,49 +5648,44 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>79435781</v>
+        <v>79438171</v>
       </c>
       <c r="B52" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6409,10 +5695,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>461641.9950303915</v>
+        <v>461440</v>
       </c>
       <c r="R52" t="n">
-        <v>7075598.56020732</v>
+        <v>7075636</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6442,21 +5728,11 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6465,68 +5741,48 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>79438175</v>
+        <v>79438172</v>
       </c>
       <c r="B53" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6536,10 +5792,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>461537.666899582</v>
+        <v>461658</v>
       </c>
       <c r="R53" t="n">
-        <v>7075570.227453075</v>
+        <v>7075600</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6569,19 +5825,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6608,37 +5854,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>79438186</v>
+        <v>79438173</v>
       </c>
       <c r="B54" t="n">
-        <v>76863</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>498</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6648,10 +5889,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>461450.5133042312</v>
+        <v>461658</v>
       </c>
       <c r="R54" t="n">
-        <v>7075607.530141714</v>
+        <v>7075623</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6681,19 +5922,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6720,37 +5951,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>79436272</v>
+        <v>79436299</v>
       </c>
       <c r="B55" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6760,10 +5986,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>461635.6827203904</v>
+        <v>461468</v>
       </c>
       <c r="R55" t="n">
-        <v>7075588.915519563</v>
+        <v>7075604</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6793,19 +6019,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6832,15 +6048,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>79437298</v>
+        <v>79436300</v>
       </c>
       <c r="B56" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6848,21 +6059,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6872,10 +6083,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>461509.5893868097</v>
+        <v>461636</v>
       </c>
       <c r="R56" t="n">
-        <v>7075553.778795606</v>
+        <v>7075590</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6905,19 +6116,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6932,49 +6133,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>79435779</v>
+        <v>79438199</v>
       </c>
       <c r="B57" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6984,10 +6180,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>461468.8793963864</v>
+        <v>461538</v>
       </c>
       <c r="R57" t="n">
-        <v>7075625.864532714</v>
+        <v>7075565</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7017,21 +6213,11 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7040,68 +6226,48 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>79435776</v>
+        <v>79438200</v>
       </c>
       <c r="B58" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7111,10 +6277,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>461456.4466579014</v>
+        <v>461588</v>
       </c>
       <c r="R58" t="n">
-        <v>7075694.509296044</v>
+        <v>7075581</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7144,21 +6310,11 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7167,68 +6323,48 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>79436270</v>
+        <v>79435793</v>
       </c>
       <c r="B59" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7238,10 +6374,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>461415.6194505997</v>
+        <v>461438</v>
       </c>
       <c r="R59" t="n">
-        <v>7075648.612075156</v>
+        <v>7075641</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7271,19 +6407,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7298,27 +6424,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>79435790</v>
+        <v>79435794</v>
       </c>
       <c r="B60" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7326,21 +6447,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2809</v>
+        <v>6464</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7350,10 +6471,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>461513.814457704</v>
+        <v>461446</v>
       </c>
       <c r="R60" t="n">
-        <v>7075573.61257309</v>
+        <v>7075631</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7383,19 +6504,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7422,37 +6533,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>79438192</v>
+        <v>79435795</v>
       </c>
       <c r="B61" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1204</v>
+        <v>6464</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7462,10 +6568,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>461519.3342660909</v>
+        <v>461449</v>
       </c>
       <c r="R61" t="n">
-        <v>7075590.779011665</v>
+        <v>7075609</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7495,19 +6601,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7522,27 +6618,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>79438183</v>
+        <v>79435796</v>
       </c>
       <c r="B62" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7574,10 +6665,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>461535.832396385</v>
+        <v>461483</v>
       </c>
       <c r="R62" t="n">
-        <v>7075564.947102019</v>
+        <v>7075588</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7607,19 +6698,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7634,27 +6715,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>79436261</v>
+        <v>79435797</v>
       </c>
       <c r="B63" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7662,21 +6738,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7686,10 +6762,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>461571.8886272095</v>
+        <v>461536</v>
       </c>
       <c r="R63" t="n">
-        <v>7075510.152188309</v>
+        <v>7075553</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7719,19 +6795,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7746,27 +6812,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+          <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>79436263</v>
+        <v>79436277</v>
       </c>
       <c r="B64" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7774,21 +6835,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7798,10 +6859,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>461478.4593544712</v>
+        <v>461508</v>
       </c>
       <c r="R64" t="n">
-        <v>7075577.13875683</v>
+        <v>7075560</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7831,19 +6892,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7870,37 +6921,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>79436256</v>
+        <v>79436278</v>
       </c>
       <c r="B65" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7910,10 +6956,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>461577.4891999869</v>
+        <v>461556</v>
       </c>
       <c r="R65" t="n">
-        <v>7075533.946643816</v>
+        <v>7075494</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7943,19 +6989,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7982,15 +7018,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>79436262</v>
+        <v>79436279</v>
       </c>
       <c r="B66" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7998,34 +7029,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Järnsjöhön, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>461421.991949006</v>
+        <v>461638</v>
       </c>
       <c r="R66" t="n">
-        <v>7075663.116167263</v>
+        <v>7075596</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8055,27 +7089,18 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -8087,44 +7112,39 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+          <t>Isak Vahlström, Linda Johannesson, Anton Gustafsson, Tore Dahlberg, Astrid Eklund</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>79438166</v>
+        <v>79437302</v>
       </c>
       <c r="B67" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8134,10 +7154,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>461580.8020457862</v>
+        <v>461514</v>
       </c>
       <c r="R67" t="n">
-        <v>7075551.582265753</v>
+        <v>7075522</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8167,19 +7187,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8206,15 +7216,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>79436287</v>
+        <v>79437303</v>
       </c>
       <c r="B68" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8222,21 +7227,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229748</v>
+        <v>6464</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8246,10 +7251,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>461465.9813299553</v>
+        <v>461409</v>
       </c>
       <c r="R68" t="n">
-        <v>7075606.014876947</v>
+        <v>7075697</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8279,19 +7284,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8306,27 +7301,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>79437305</v>
+        <v>79437304</v>
       </c>
       <c r="B69" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8358,10 +7348,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>461551.2514887589</v>
+        <v>461509</v>
       </c>
       <c r="R69" t="n">
-        <v>7075523.219717619</v>
+        <v>7075556</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8391,19 +7381,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8430,15 +7410,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>79436266</v>
+        <v>79437305</v>
       </c>
       <c r="B70" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8446,21 +7421,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8470,10 +7445,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>461630.3845801949</v>
+        <v>461551</v>
       </c>
       <c r="R70" t="n">
-        <v>7075589.863952381</v>
+        <v>7075523</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8503,19 +7478,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8530,27 +7495,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>79435795</v>
+        <v>79438183</v>
       </c>
       <c r="B71" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8582,10 +7542,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>461449.2023307998</v>
+        <v>461536</v>
       </c>
       <c r="R71" t="n">
-        <v>7075608.871894378</v>
+        <v>7075565</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8615,19 +7575,9 @@
           <t>2019-08-10</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2019-08-10</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8642,15 +7592,1087 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>79438184</v>
+      </c>
+      <c r="B72" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Järnsjöhön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>461584</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7075588</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2019-08-10</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2019-08-10</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>79436283</v>
+      </c>
+      <c r="B73" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Järnsjöhön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>461502</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7075567</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2019-08-10</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2019-08-10</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>79435799</v>
+      </c>
+      <c r="B74" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Järnsjöhön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>461503</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7075565</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2019-08-10</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2019-08-10</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
           <t>Isak Vahlström</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
+      <c r="AX74" t="inlineStr">
         <is>
           <t>Isak Vahlström, Linda Johannesson, Tore Dahlberg, Astrid Eklund, Anton Gustafsson, Charlotta Leineweber</t>
         </is>
       </c>
-      <c r="AY71" t="inlineStr"/>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>79436282</v>
+      </c>
+      <c r="B75" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Järnsjöhön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>461634</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7075593</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2019-08-10</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2019-08-10</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>79436284</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Järnsjöhön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>461623</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7075581</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2019-08-10</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2019-08-10</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>79436267</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Järnsjöhön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>461459</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7075601</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2019-08-10</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2019-08-10</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>79436287</v>
+      </c>
+      <c r="B78" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Järnsjöhön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>461466</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7075606</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2019-08-10</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2019-08-10</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>79436288</v>
+      </c>
+      <c r="B79" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Järnsjöhön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>461627</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7075577</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2019-08-10</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2019-08-10</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg, Isak Vahlström, Linda Johannesson, Anton Gustafsson, Astrid Eklund</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79437307</v>
+      </c>
+      <c r="B80" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Järnsjöhön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>461409</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7075696</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2019-08-10</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2019-08-10</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>79438189</v>
+      </c>
+      <c r="B81" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Järnsjöhön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>461570</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7075555</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2019-08-10</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2019-08-10</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>79438190</v>
+      </c>
+      <c r="B82" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Järnsjöhön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>461580</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7075588</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2019-08-10</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2019-08-10</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Isak Vahlström, Astrid Eklund, Tore Dahlberg, Anton Gustafsson, Adam Bergström, Charlotta Leineweber</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33846-2023 artfynd.xlsx
+++ b/artfynd/A 33846-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY82"/>
+  <dimension ref="A1:AZ82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79438174</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79435824</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79438186</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79435823</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79438187</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79435806</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79436289</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1478,6 +1518,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79438191</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1575,6 +1620,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79438192</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1672,6 +1722,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79436296</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1769,6 +1824,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79435789</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1866,6 +1926,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79436270</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1963,6 +2028,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79436271</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2060,6 +2130,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79436272</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2157,6 +2232,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79437300</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2254,6 +2334,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79438175</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2351,6 +2436,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79438176</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2448,6 +2538,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79435790</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2560,6 +2655,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79435786</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2657,6 +2757,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79435815</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2754,6 +2859,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79435816</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2851,6 +2961,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79435817</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2963,6 +3078,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79435776</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3075,6 +3195,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79435777</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3187,6 +3312,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79435778</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3299,6 +3429,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79435779</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3411,6 +3546,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79435780</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3523,6 +3663,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79435781</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3620,6 +3765,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79436254</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3717,6 +3867,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79436255</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3814,6 +3969,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79436256</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3911,6 +4071,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79437700</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4008,6 +4173,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79437706</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4105,6 +4275,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79437707</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4202,6 +4377,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79438165</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4299,6 +4479,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79438166</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4396,6 +4581,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79438167</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4493,6 +4683,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79436275</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4590,6 +4785,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79435787</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4687,6 +4887,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79436259</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4784,6 +4989,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79436260</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4881,6 +5091,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79436261</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4978,6 +5193,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79436262</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5075,6 +5295,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79436263</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5172,6 +5397,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79436264</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5269,6 +5499,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79436265</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5366,6 +5601,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79436266</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5463,6 +5703,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79437296</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5560,6 +5805,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79437297</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5657,6 +5907,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79437298</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5754,6 +6009,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79438171</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5851,6 +6111,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79438172</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5948,6 +6213,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79438173</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6045,6 +6315,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79436299</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6142,6 +6417,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79436300</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6239,6 +6519,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79438199</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6336,6 +6621,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79438200</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6433,6 +6723,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79435793</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6530,6 +6825,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79435794</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6627,6 +6927,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79435795</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6724,6 +7029,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79435796</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6821,6 +7131,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79435797</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6918,6 +7233,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79436277</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7015,6 +7335,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79436278</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7116,6 +7441,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79436279</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7213,6 +7543,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79437302</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7310,6 +7645,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79437303</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7407,6 +7747,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79437304</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7504,6 +7849,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79437305</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7601,6 +7951,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79438183</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7698,6 +8053,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79438184</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7795,6 +8155,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79436283</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7897,6 +8262,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79435799</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7994,6 +8364,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79436282</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8091,6 +8466,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79436284</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8188,6 +8568,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79436267</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8285,6 +8670,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79436287</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8382,6 +8772,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79436288</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8479,6 +8874,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79437307</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8576,6 +8976,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79438189</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8673,8 +9078,96 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79438190</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>